--- a/phase5_1/input/item_spread.xlsx
+++ b/phase5_1/input/item_spread.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Item ID</t>
   </si>
@@ -34,6 +34,18 @@
   </si>
   <si>
     <t>DEMO-004</t>
+  </si>
+  <si>
+    <t>584-LT1076HVIR#PBF</t>
+  </si>
+  <si>
+    <t>457-REX22DTA116E</t>
+  </si>
+  <si>
+    <t>571-10219128-02</t>
+  </si>
+  <si>
+    <t>225-DCM30V10L20S1PFB</t>
   </si>
 </sst>
 </file>
@@ -840,8 +852,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -868,6 +883,26 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
